--- a/research/traditional_assets/database/data/oman/oman_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0483</v>
+        <v>0.00848</v>
       </c>
       <c r="E2">
-        <v>-0.163</v>
+        <v>-0.05405</v>
       </c>
       <c r="G2">
-        <v>0.4299264071868295</v>
+        <v>0.1910935738444194</v>
       </c>
       <c r="H2">
-        <v>0.4299264071868295</v>
+        <v>0.1910935738444194</v>
       </c>
       <c r="I2">
-        <v>0.1975174958390984</v>
+        <v>0.2872455907471557</v>
       </c>
       <c r="J2">
-        <v>0.1791555157863352</v>
+        <v>0.2470731469178301</v>
       </c>
       <c r="K2">
-        <v>89.50200000000001</v>
+        <v>181.43</v>
       </c>
       <c r="L2">
-        <v>0.1794742224628527</v>
+        <v>0.2556792559188275</v>
       </c>
       <c r="M2">
-        <v>59.74</v>
+        <v>80.6228</v>
       </c>
       <c r="N2">
-        <v>0.07753406878650228</v>
+        <v>0.06758554782462906</v>
       </c>
       <c r="O2">
-        <v>0.6674711179638443</v>
+        <v>0.4443741387863087</v>
       </c>
       <c r="P2">
-        <v>59.74</v>
+        <v>79.58279999999999</v>
       </c>
       <c r="Q2">
-        <v>0.07753406878650228</v>
+        <v>0.06671372286025652</v>
       </c>
       <c r="R2">
-        <v>0.6674711179638443</v>
+        <v>0.4386419004574766</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.039999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01289957679465361</v>
       </c>
       <c r="U2">
-        <v>243.05</v>
+        <v>446.19</v>
       </c>
       <c r="V2">
-        <v>0.3154445165476963</v>
+        <v>0.3740380585128679</v>
       </c>
       <c r="W2">
-        <v>0.04077017114914425</v>
+        <v>0.0607239081743594</v>
       </c>
       <c r="X2">
-        <v>0.06484371544387532</v>
+        <v>0.09199344818345505</v>
       </c>
       <c r="Y2">
-        <v>-0.02407354429473107</v>
+        <v>-0.03126954000909565</v>
       </c>
       <c r="Z2">
-        <v>0.2132247306310928</v>
+        <v>0.2126268054440837</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.170473438630387e-05</v>
       </c>
       <c r="AB2">
-        <v>0.05090361300764507</v>
+        <v>0.0849664285977049</v>
       </c>
       <c r="AC2">
-        <v>-0.05003511614478781</v>
+        <v>-0.0849664285977049</v>
       </c>
       <c r="AD2">
-        <v>803.8</v>
+        <v>2792.1</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.03264402909178637</v>
       </c>
       <c r="AF2">
-        <v>803.8</v>
+        <v>2792.132644029092</v>
       </c>
       <c r="AG2">
-        <v>560.75</v>
+        <v>2345.942644029092</v>
       </c>
       <c r="AH2">
-        <v>0.5105761290732389</v>
+        <v>0.7006548988281533</v>
       </c>
       <c r="AI2">
-        <v>0.6175476336816226</v>
+        <v>0.5916371772525302</v>
       </c>
       <c r="AJ2">
-        <v>0.4212206572769953</v>
+        <v>0.6629123925550295</v>
       </c>
       <c r="AK2">
-        <v>0.5297340701903548</v>
+        <v>0.5489970355441101</v>
       </c>
       <c r="AL2">
-        <v>52.3</v>
+        <v>58.7</v>
       </c>
       <c r="AM2">
-        <v>52.3</v>
+        <v>58.7</v>
       </c>
       <c r="AN2">
-        <v>7.819066147859921</v>
+        <v>13.26186495421211</v>
       </c>
       <c r="AO2">
-        <v>1.883365200764818</v>
+        <v>3.471890971039182</v>
       </c>
       <c r="AP2">
-        <v>5.45476653696498</v>
+        <v>11.14271499424845</v>
       </c>
       <c r="AQ2">
-        <v>1.883365200764818</v>
+        <v>3.471890971039182</v>
       </c>
     </row>
     <row r="3">
@@ -722,115 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00045</v>
+        <v>0.0344</v>
       </c>
       <c r="E3">
-        <v>0.08699999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="G3">
-        <v>0.4596317280453257</v>
+        <v>0.2136648122392211</v>
       </c>
       <c r="H3">
-        <v>0.4596317280453257</v>
+        <v>0.2136648122392211</v>
       </c>
       <c r="I3">
-        <v>0.1916902738432484</v>
+        <v>0.3329276773296245</v>
       </c>
       <c r="J3">
-        <v>0.1816840871349028</v>
+        <v>0.3274569190493005</v>
       </c>
       <c r="K3">
-        <v>74.7</v>
+        <v>132.1</v>
       </c>
       <c r="L3">
-        <v>0.1763456090651558</v>
+        <v>0.2296592489568845</v>
       </c>
       <c r="M3">
-        <v>56.7</v>
+        <v>59.34</v>
       </c>
       <c r="N3">
-        <v>0.1066992849077908</v>
+        <v>0.08119868637110017</v>
       </c>
       <c r="O3">
-        <v>0.7590361445783133</v>
+        <v>0.4492051476154428</v>
       </c>
       <c r="P3">
-        <v>56.7</v>
+        <v>58.3</v>
       </c>
       <c r="Q3">
-        <v>0.1066992849077908</v>
+        <v>0.07977558839627805</v>
       </c>
       <c r="R3">
-        <v>0.7590361445783133</v>
+        <v>0.441332323996972</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.039999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01752612066059992</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>184.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.2519157088122606</v>
       </c>
       <c r="W3">
-        <v>0.1110615521855486</v>
+        <v>0.1836252432582708</v>
       </c>
       <c r="X3">
-        <v>0.02991503512048407</v>
+        <v>0.08514595762475913</v>
       </c>
       <c r="Y3">
-        <v>0.08114651706506454</v>
+        <v>0.09847928563351166</v>
       </c>
       <c r="Z3">
-        <v>0.3705388383484954</v>
+        <v>0.4443757725587145</v>
       </c>
       <c r="AA3">
-        <v>0.0673210105933737</v>
+        <v>0.1455139213822293</v>
       </c>
       <c r="AB3">
-        <v>0.02991503512048407</v>
+        <v>0.08042845131752813</v>
       </c>
       <c r="AC3">
-        <v>0.03740597547288963</v>
+        <v>0.06508547006470122</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1222.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1222.9</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1038.8</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.6259405231099965</v>
+      </c>
+      <c r="AI3">
+        <v>0.5229196955443427</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.5870253164556962</v>
+      </c>
+      <c r="AK3">
+        <v>0.4821536319331632</v>
       </c>
       <c r="AL3">
-        <v>39.7</v>
+        <v>47.2</v>
       </c>
       <c r="AM3">
-        <v>39.7</v>
+        <v>47.2</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>6.179383527033856</v>
       </c>
       <c r="AO3">
-        <v>2.045340050377834</v>
+        <v>4.057203389830509</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>5.24911571500758</v>
       </c>
       <c r="AQ3">
-        <v>2.045340050377834</v>
+        <v>4.057203389830509</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0483</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="E4">
-        <v>-0.163</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="G4">
-        <v>0.493734335839599</v>
+        <v>0.4057507987220447</v>
       </c>
       <c r="H4">
-        <v>0.493734335839599</v>
+        <v>0.4057507987220447</v>
       </c>
       <c r="I4">
-        <v>0.4335839598997494</v>
+        <v>0.3929712460063898</v>
       </c>
       <c r="J4">
-        <v>0.4086850790342192</v>
+        <v>0.3343743501521825</v>
       </c>
       <c r="K4">
-        <v>6.67</v>
+        <v>7.18</v>
       </c>
       <c r="L4">
-        <v>0.1671679197994987</v>
+        <v>0.2293929712460064</v>
       </c>
       <c r="M4">
-        <v>3.04</v>
+        <v>5.31</v>
       </c>
       <c r="N4">
-        <v>0.03311546840958605</v>
+        <v>0.0439569536423841</v>
       </c>
       <c r="O4">
-        <v>0.4557721139430285</v>
+        <v>0.7395543175487465</v>
       </c>
       <c r="P4">
-        <v>3.04</v>
+        <v>5.31</v>
       </c>
       <c r="Q4">
-        <v>0.03311546840958605</v>
+        <v>0.0439569536423841</v>
       </c>
       <c r="R4">
-        <v>0.4557721139430285</v>
+        <v>0.7395543175487465</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>221.9</v>
+        <v>221.3</v>
       </c>
       <c r="V4">
-        <v>2.417211328976035</v>
+        <v>1.831953642384106</v>
       </c>
       <c r="W4">
-        <v>0.04077017114914425</v>
+        <v>0.04284009546539379</v>
       </c>
       <c r="X4">
-        <v>0.07056035832603434</v>
+        <v>0.0970005476139239</v>
       </c>
       <c r="Y4">
-        <v>-0.02979018717689009</v>
+        <v>-0.05416045214853011</v>
       </c>
       <c r="Z4">
-        <v>0.1413890857547838</v>
+        <v>0.1253002401921537</v>
       </c>
       <c r="AA4">
-        <v>0.05778360968626983</v>
+        <v>0.04189718638816377</v>
       </c>
       <c r="AB4">
-        <v>0.05171614587436327</v>
+        <v>0.08330871488296746</v>
       </c>
       <c r="AC4">
-        <v>0.006067463811906558</v>
+        <v>-0.04141152849480368</v>
       </c>
       <c r="AD4">
-        <v>296.3</v>
+        <v>290.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>296.3</v>
+        <v>290.2</v>
       </c>
       <c r="AG4">
-        <v>74.40000000000001</v>
+        <v>68.89999999999998</v>
       </c>
       <c r="AH4">
-        <v>0.7634630249935583</v>
+        <v>0.7060827250608273</v>
       </c>
       <c r="AI4">
-        <v>0.6387152403535246</v>
+        <v>0.6293645630015181</v>
       </c>
       <c r="AJ4">
-        <v>0.4476534296028882</v>
+        <v>0.3632050606220347</v>
       </c>
       <c r="AK4">
-        <v>0.3074380165289257</v>
+        <v>0.287322768974145</v>
       </c>
       <c r="AL4">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="AM4">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="AN4">
-        <v>16.83522727272727</v>
+        <v>23.03174603174603</v>
       </c>
       <c r="AO4">
-        <v>1.373015873015873</v>
+        <v>1.069565217391304</v>
       </c>
       <c r="AP4">
-        <v>4.227272727272728</v>
+        <v>5.468253968253967</v>
       </c>
       <c r="AQ4">
-        <v>1.373015873015873</v>
+        <v>1.069565217391304</v>
       </c>
     </row>
     <row r="5">
@@ -984,10 +990,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.159</v>
+        <v>0.0148</v>
       </c>
       <c r="E5">
-        <v>-0.31</v>
+        <v>-0.031</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1002,82 +1008,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1.93</v>
+        <v>6.14</v>
       </c>
       <c r="L5">
-        <v>0.1989690721649485</v>
+        <v>0.374390243902439</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>2.7928</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04519093851132686</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.4548534201954398</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2.7928</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.04519093851132686</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4548534201954398</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="V5">
-        <v>0.02560747663551402</v>
+        <v>0.0168284789644013</v>
       </c>
       <c r="W5">
-        <v>0.01641156462585034</v>
+        <v>0.05125208681135225</v>
       </c>
       <c r="X5">
-        <v>0.04686232763214061</v>
+        <v>0.08103704437686482</v>
       </c>
       <c r="Y5">
-        <v>-0.03045076300629027</v>
+        <v>-0.02978495756551257</v>
       </c>
       <c r="Z5">
-        <v>0.04652055057311399</v>
+        <v>0.08612088431444624</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05003511614478781</v>
+        <v>0.08476223205805308</v>
       </c>
       <c r="AC5">
-        <v>-0.05003511614478781</v>
+        <v>-0.08476223205805308</v>
       </c>
       <c r="AD5">
-        <v>72</v>
+        <v>87.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>72</v>
+        <v>87.8</v>
       </c>
       <c r="AG5">
-        <v>70.63</v>
+        <v>86.75999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.5737051792828686</v>
+        <v>0.5868983957219251</v>
       </c>
       <c r="AI5">
-        <v>0.3753910323253389</v>
+        <v>0.4167062173706692</v>
       </c>
       <c r="AJ5">
-        <v>0.5690002416821075</v>
+        <v>0.5840064620355411</v>
       </c>
       <c r="AK5">
-        <v>0.3708974426298377</v>
+        <v>0.4138128398359248</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1103,10 +1112,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.189</v>
+        <v>-0.131</v>
       </c>
       <c r="E6">
-        <v>-0.466</v>
+        <v>-0.251</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1121,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.492</v>
+        <v>2.92</v>
       </c>
       <c r="L6">
-        <v>0.06482213438735178</v>
+        <v>0.2703703703703704</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1148,55 +1157,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="V6">
-        <v>0.05775862068965518</v>
+        <v>0.04903846153846154</v>
       </c>
       <c r="W6">
-        <v>0.005046153846153846</v>
+        <v>0.02979591836734694</v>
       </c>
       <c r="X6">
-        <v>0.06484371544387532</v>
+        <v>0.08698634875298619</v>
       </c>
       <c r="Y6">
-        <v>-0.05979756159772148</v>
+        <v>-0.05719043038563926</v>
       </c>
       <c r="Z6">
-        <v>0.02721795883238901</v>
+        <v>0.04820998125167397</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05090361300764507</v>
+        <v>0.08517062513735672</v>
       </c>
       <c r="AC6">
-        <v>-0.05090361300764507</v>
+        <v>-0.08517062513735672</v>
       </c>
       <c r="AD6">
-        <v>128.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>128.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AG6">
-        <v>126.02</v>
+        <v>90.35000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.7350085665334094</v>
+        <v>0.6411318150448585</v>
       </c>
       <c r="AI6">
-        <v>0.5677106307895897</v>
+        <v>0.4801033591731266</v>
       </c>
       <c r="AJ6">
-        <v>0.730889687971233</v>
+        <v>0.6347031963470319</v>
       </c>
       <c r="AK6">
-        <v>0.5625390590125882</v>
+        <v>0.4731605132233569</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1213,114 +1222,245 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>National Finance Company SAOG (MSM:NFCI)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.15</v>
+      </c>
+      <c r="E7">
+        <v>0.104</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.0005488118097140172</v>
+      </c>
+      <c r="J7">
+        <v>0.0004257090991658576</v>
+      </c>
+      <c r="K7">
+        <v>25.2</v>
+      </c>
+      <c r="L7">
+        <v>0.4692737430167597</v>
+      </c>
+      <c r="M7">
+        <v>11.2</v>
+      </c>
+      <c r="N7">
+        <v>0.06926406926406926</v>
+      </c>
+      <c r="O7">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P7">
+        <v>11.2</v>
+      </c>
+      <c r="Q7">
+        <v>0.06926406926406926</v>
+      </c>
+      <c r="R7">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>13</v>
+      </c>
+      <c r="V7">
+        <v>0.08039579468150897</v>
+      </c>
+      <c r="W7">
+        <v>0.08823529411764705</v>
+      </c>
+      <c r="X7">
+        <v>0.1325609006105203</v>
+      </c>
+      <c r="Y7">
+        <v>-0.04432560649287323</v>
+      </c>
+      <c r="Z7">
+        <v>0.05498935498084655</v>
+      </c>
+      <c r="AA7">
+        <v>2.340946877260775e-05</v>
+      </c>
+      <c r="AB7">
+        <v>0.09546749606226292</v>
+      </c>
+      <c r="AC7">
+        <v>-0.09544408659349031</v>
+      </c>
+      <c r="AD7">
+        <v>742</v>
+      </c>
+      <c r="AE7">
+        <v>0.03264402909178637</v>
+      </c>
+      <c r="AF7">
+        <v>742.0326440290918</v>
+      </c>
+      <c r="AG7">
+        <v>729.0326440290918</v>
+      </c>
+      <c r="AH7">
+        <v>0.8210754020358318</v>
+      </c>
+      <c r="AI7">
+        <v>0.7129906496988382</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8184640463286773</v>
+      </c>
+      <c r="AK7">
+        <v>0.709360209841165</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>20611.11111111111</v>
+      </c>
+      <c r="AP7">
+        <v>20250.90677858589</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Taageer Finance Company SAOG (MSM:TFCI)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.0367</v>
-      </c>
-      <c r="E7">
-        <v>-0.132</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>5.71</v>
-      </c>
-      <c r="L7">
-        <v>0.3189944134078213</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>17.1</v>
-      </c>
-      <c r="V7">
-        <v>0.3607594936708861</v>
-      </c>
-      <c r="W7">
-        <v>0.05346441947565543</v>
-      </c>
-      <c r="X7">
-        <v>0.1114227325618308</v>
-      </c>
-      <c r="Y7">
-        <v>-0.05795831308617538</v>
-      </c>
-      <c r="Z7">
-        <v>0.04201582048212567</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05464920907852542</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05464920907852542</v>
-      </c>
-      <c r="AD7">
-        <v>306.8</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>306.8</v>
-      </c>
-      <c r="AG7">
-        <v>289.7</v>
-      </c>
-      <c r="AH7">
-        <v>0.8661773009599097</v>
-      </c>
-      <c r="AI7">
-        <v>0.7318702290076335</v>
-      </c>
-      <c r="AJ7">
-        <v>0.8593889053693267</v>
-      </c>
-      <c r="AK7">
-        <v>0.7204675453867196</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
+      <c r="D8">
+        <v>0.00216</v>
+      </c>
+      <c r="E8">
+        <v>-0.0771</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>7.89</v>
+      </c>
+      <c r="L8">
+        <v>0.3554054054054054</v>
+      </c>
+      <c r="M8">
+        <v>1.98</v>
+      </c>
+      <c r="N8">
+        <v>0.03009118541033435</v>
+      </c>
+      <c r="O8">
+        <v>0.2509505703422053</v>
+      </c>
+      <c r="P8">
+        <v>1.98</v>
+      </c>
+      <c r="Q8">
+        <v>0.03009118541033435</v>
+      </c>
+      <c r="R8">
+        <v>0.2509505703422053</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>24.2</v>
+      </c>
+      <c r="V8">
+        <v>0.3677811550151976</v>
+      </c>
+      <c r="W8">
+        <v>0.07019572953736654</v>
+      </c>
+      <c r="X8">
+        <v>0.1459929815323023</v>
+      </c>
+      <c r="Y8">
+        <v>-0.07579725199493574</v>
+      </c>
+      <c r="Z8">
+        <v>0.05521014672966923</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.09652063575516864</v>
+      </c>
+      <c r="AC8">
+        <v>-0.09652063575516864</v>
+      </c>
+      <c r="AD8">
+        <v>356.3</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>356.3</v>
+      </c>
+      <c r="AG8">
+        <v>332.1</v>
+      </c>
+      <c r="AH8">
+        <v>0.8441127694859037</v>
+      </c>
+      <c r="AI8">
+        <v>0.7505793132504739</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8346318170394571</v>
+      </c>
+      <c r="AK8">
+        <v>0.7371809100998891</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/oman/oman_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00848</v>
+        <v>0.040325</v>
       </c>
       <c r="E2">
-        <v>-0.05405</v>
+        <v>-0.0267</v>
+      </c>
+      <c r="F2">
+        <v>0.092</v>
       </c>
       <c r="G2">
-        <v>0.1910935738444194</v>
+        <v>0.1432445067788686</v>
       </c>
       <c r="H2">
-        <v>0.1910935738444194</v>
+        <v>0.1432445067788686</v>
       </c>
       <c r="I2">
-        <v>0.2872455907471557</v>
+        <v>0.1137215690743794</v>
       </c>
       <c r="J2">
-        <v>0.2470731469178301</v>
+        <v>0.1020288179781876</v>
       </c>
       <c r="K2">
-        <v>181.43</v>
+        <v>138.448</v>
       </c>
       <c r="L2">
-        <v>0.2556792559188275</v>
+        <v>0.1294511453950444</v>
       </c>
       <c r="M2">
-        <v>80.6228</v>
+        <v>223.46</v>
       </c>
       <c r="N2">
-        <v>0.06758554782462906</v>
+        <v>0.1737500971930643</v>
       </c>
       <c r="O2">
-        <v>0.4443741387863087</v>
+        <v>1.614035594591471</v>
       </c>
       <c r="P2">
-        <v>79.58279999999999</v>
+        <v>50.36</v>
       </c>
       <c r="Q2">
-        <v>0.06671372286025652</v>
+        <v>0.03915714174636498</v>
       </c>
       <c r="R2">
-        <v>0.4386419004574766</v>
+        <v>0.3637466774529065</v>
       </c>
       <c r="S2">
-        <v>1.039999999999999</v>
+        <v>173.1</v>
       </c>
       <c r="T2">
-        <v>0.01289957679465361</v>
+        <v>0.7746352814821446</v>
       </c>
       <c r="U2">
-        <v>446.19</v>
+        <v>559.9</v>
       </c>
       <c r="V2">
-        <v>0.3740380585128679</v>
+        <v>0.4353471736256901</v>
       </c>
       <c r="W2">
-        <v>0.0607239081743594</v>
+        <v>0.06546299993674189</v>
       </c>
       <c r="X2">
-        <v>0.09199344818345505</v>
+        <v>0.1009596191132385</v>
       </c>
       <c r="Y2">
-        <v>-0.03126954000909565</v>
+        <v>-0.03549661917649659</v>
       </c>
       <c r="Z2">
-        <v>0.2126268054440837</v>
+        <v>0.2737997866469095</v>
       </c>
       <c r="AA2">
-        <v>1.170473438630387e-05</v>
+        <v>1.058822075370079e-05</v>
       </c>
       <c r="AB2">
-        <v>0.0849664285977049</v>
+        <v>0.07576586691393239</v>
       </c>
       <c r="AC2">
-        <v>-0.0849664285977049</v>
+        <v>-0.07317343347990318</v>
       </c>
       <c r="AD2">
-        <v>2792.1</v>
+        <v>3195.5</v>
       </c>
       <c r="AE2">
-        <v>0.03264402909178637</v>
+        <v>0.028909374756027</v>
       </c>
       <c r="AF2">
-        <v>2792.132644029092</v>
+        <v>3195.528909374756</v>
       </c>
       <c r="AG2">
-        <v>2345.942644029092</v>
+        <v>2635.628909374756</v>
       </c>
       <c r="AH2">
-        <v>0.7006548988281533</v>
+        <v>0.7130284488058098</v>
       </c>
       <c r="AI2">
-        <v>0.5916371772525302</v>
+        <v>0.6417589533718936</v>
       </c>
       <c r="AJ2">
-        <v>0.6629123925550295</v>
+        <v>0.6720579036134745</v>
       </c>
       <c r="AK2">
-        <v>0.5489970355441101</v>
+        <v>0.5963731883510792</v>
       </c>
       <c r="AL2">
-        <v>58.7</v>
+        <v>74.5</v>
       </c>
       <c r="AM2">
-        <v>58.7</v>
+        <v>74.5</v>
       </c>
       <c r="AN2">
-        <v>13.26186495421211</v>
+        <v>24.2209943076305</v>
       </c>
       <c r="AO2">
-        <v>3.471890971039182</v>
+        <v>1.632214765100671</v>
       </c>
       <c r="AP2">
-        <v>11.14271499424845</v>
+        <v>19.97732837145747</v>
       </c>
       <c r="AQ2">
-        <v>3.471890971039182</v>
+        <v>1.632214765100671</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oman International Development and Investment Company SAOG (MSM:OMVS)</t>
+          <t>Al Omaniya Financial Services SAOG (MSM:AOFS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0344</v>
+        <v>-0.0365</v>
       </c>
       <c r="E3">
-        <v>0.144</v>
+        <v>-0.138</v>
       </c>
       <c r="G3">
-        <v>0.2136648122392211</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="H3">
-        <v>0.2136648122392211</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="I3">
-        <v>0.3329276773296245</v>
+        <v>0.5051020408163265</v>
       </c>
       <c r="J3">
-        <v>0.3274569190493005</v>
+        <v>0.429175188198947</v>
       </c>
       <c r="K3">
-        <v>132.1</v>
+        <v>7.97</v>
       </c>
       <c r="L3">
-        <v>0.2296592489568845</v>
+        <v>0.2033163265306122</v>
       </c>
       <c r="M3">
-        <v>59.34</v>
+        <v>5.71</v>
       </c>
       <c r="N3">
-        <v>0.08119868637110017</v>
+        <v>0.04329037149355573</v>
       </c>
       <c r="O3">
-        <v>0.4492051476154428</v>
+        <v>0.7164366373902133</v>
       </c>
       <c r="P3">
-        <v>58.3</v>
+        <v>5.71</v>
       </c>
       <c r="Q3">
-        <v>0.07977558839627805</v>
+        <v>0.04329037149355573</v>
       </c>
       <c r="R3">
-        <v>0.441332323996972</v>
+        <v>0.7164366373902133</v>
       </c>
       <c r="S3">
-        <v>1.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01752612066059992</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>184.1</v>
+        <v>221</v>
       </c>
       <c r="V3">
-        <v>0.2519157088122606</v>
+        <v>1.675511751326763</v>
       </c>
       <c r="W3">
-        <v>0.1836252432582708</v>
+        <v>0.04663545933294324</v>
       </c>
       <c r="X3">
-        <v>0.08514595762475913</v>
+        <v>0.1034558230228052</v>
       </c>
       <c r="Y3">
-        <v>0.09847928563351166</v>
+        <v>-0.05682036368986194</v>
       </c>
       <c r="Z3">
-        <v>0.4443757725587145</v>
+        <v>0.1634695579649708</v>
       </c>
       <c r="AA3">
-        <v>0.1455139213822293</v>
+        <v>0.07015707830441502</v>
       </c>
       <c r="AB3">
-        <v>0.08042845131752813</v>
+        <v>0.07815951192136038</v>
       </c>
       <c r="AC3">
-        <v>0.06508547006470122</v>
+        <v>-0.008002433616945359</v>
       </c>
       <c r="AD3">
-        <v>1222.9</v>
+        <v>351.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1222.9</v>
+        <v>351.9</v>
       </c>
       <c r="AG3">
-        <v>1038.8</v>
+        <v>130.9</v>
       </c>
       <c r="AH3">
-        <v>0.6259405231099965</v>
+        <v>0.7273666804464655</v>
       </c>
       <c r="AI3">
-        <v>0.5229196955443427</v>
+        <v>0.6724632142174661</v>
       </c>
       <c r="AJ3">
-        <v>0.5870253164556962</v>
+        <v>0.4980974124809741</v>
       </c>
       <c r="AK3">
-        <v>0.4821536319331632</v>
+        <v>0.4330135626860734</v>
       </c>
       <c r="AL3">
-        <v>47.2</v>
+        <v>3.4</v>
       </c>
       <c r="AM3">
-        <v>47.2</v>
+        <v>3.4</v>
       </c>
       <c r="AN3">
-        <v>6.179383527033856</v>
+        <v>17.50746268656716</v>
       </c>
       <c r="AO3">
-        <v>4.057203389830509</v>
+        <v>5.823529411764707</v>
       </c>
       <c r="AP3">
-        <v>5.24911571500758</v>
+        <v>6.512437810945272</v>
       </c>
       <c r="AQ3">
-        <v>4.057203389830509</v>
+        <v>5.823529411764707</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al Omaniya Financial Services SAOG (MSM:AOFS)</t>
+          <t>Oman International Development and Investment Company SAOG (MSM:OMVS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +859,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.09119999999999999</v>
+        <v>0.117</v>
       </c>
       <c r="E4">
-        <v>-0.09949999999999999</v>
+        <v>0.058</v>
       </c>
       <c r="G4">
-        <v>0.4057507987220447</v>
+        <v>0.1512338938632889</v>
       </c>
       <c r="H4">
-        <v>0.4057507987220447</v>
+        <v>0.1512338938632889</v>
       </c>
       <c r="I4">
-        <v>0.3929712460063898</v>
+        <v>0.1111596418431972</v>
       </c>
       <c r="J4">
-        <v>0.3343743501521825</v>
+        <v>0.1093917711090777</v>
       </c>
       <c r="K4">
-        <v>7.18</v>
+        <v>85.5</v>
       </c>
       <c r="L4">
-        <v>0.2293929712460064</v>
+        <v>0.09336099585062241</v>
       </c>
       <c r="M4">
-        <v>5.31</v>
+        <v>200.7</v>
       </c>
       <c r="N4">
-        <v>0.0439569536423841</v>
+        <v>0.2688546550569323</v>
       </c>
       <c r="O4">
-        <v>0.7395543175487465</v>
+        <v>2.347368421052631</v>
       </c>
       <c r="P4">
-        <v>5.31</v>
+        <v>27.6</v>
       </c>
       <c r="Q4">
-        <v>0.0439569536423841</v>
+        <v>0.03697253851306095</v>
       </c>
       <c r="R4">
-        <v>0.7395543175487465</v>
+        <v>0.3228070175438597</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>173.1</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.8624813153961136</v>
       </c>
       <c r="U4">
-        <v>221.3</v>
+        <v>273</v>
       </c>
       <c r="V4">
-        <v>1.831953642384106</v>
+        <v>0.3657066309444073</v>
       </c>
       <c r="W4">
-        <v>0.04284009546539379</v>
+        <v>0.09799426934097422</v>
       </c>
       <c r="X4">
-        <v>0.0970005476139239</v>
+        <v>0.08902553374478853</v>
       </c>
       <c r="Y4">
-        <v>-0.05416045214853011</v>
+        <v>0.00896873559618569</v>
       </c>
       <c r="Z4">
-        <v>0.1253002401921537</v>
+        <v>0.5079312257348862</v>
       </c>
       <c r="AA4">
-        <v>0.04189718638816377</v>
+        <v>0.05556349638474396</v>
       </c>
       <c r="AB4">
-        <v>0.08330871488296746</v>
+        <v>0.07591926750003464</v>
       </c>
       <c r="AC4">
-        <v>-0.04141152849480368</v>
+        <v>-0.02035577111529068</v>
       </c>
       <c r="AD4">
-        <v>290.2</v>
+        <v>1351.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>290.2</v>
+        <v>1351.1</v>
       </c>
       <c r="AG4">
-        <v>68.89999999999998</v>
+        <v>1078.1</v>
       </c>
       <c r="AH4">
-        <v>0.7060827250608273</v>
+        <v>0.6441170861937452</v>
       </c>
       <c r="AI4">
-        <v>0.6293645630015181</v>
+        <v>0.5763832600998251</v>
       </c>
       <c r="AJ4">
-        <v>0.3632050606220347</v>
+        <v>0.5908692316124082</v>
       </c>
       <c r="AK4">
-        <v>0.287322768974145</v>
+        <v>0.5205446381150113</v>
       </c>
       <c r="AL4">
-        <v>11.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AM4">
-        <v>11.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AN4">
-        <v>23.03174603174603</v>
+        <v>12.08497316636852</v>
       </c>
       <c r="AO4">
-        <v>1.069565217391304</v>
+        <v>1.431786216596343</v>
       </c>
       <c r="AP4">
-        <v>5.468253968253967</v>
+        <v>9.643112701252235</v>
       </c>
       <c r="AQ4">
-        <v>1.069565217391304</v>
+        <v>1.431786216596343</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>United Finance Company SAOG (MSM:UFCI)</t>
+          <t>Muscat Finance SAOG (MSM:MFCI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,10 +993,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0148</v>
+        <v>-0.114</v>
       </c>
       <c r="E5">
-        <v>-0.031</v>
+        <v>-0.4</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1008,85 +1011,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>6.14</v>
+        <v>0.758</v>
       </c>
       <c r="L5">
-        <v>0.374390243902439</v>
+        <v>0.07084112149532711</v>
       </c>
       <c r="M5">
-        <v>2.7928</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04519093851132686</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4548534201954398</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>2.7928</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.04519093851132686</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4548534201954398</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="V5">
-        <v>0.0168284789644013</v>
+        <v>0.06554216867469879</v>
       </c>
       <c r="W5">
-        <v>0.05125208681135225</v>
+        <v>0.00753479125248509</v>
       </c>
       <c r="X5">
-        <v>0.08103704437686482</v>
+        <v>0.09846341520367177</v>
       </c>
       <c r="Y5">
-        <v>-0.02978495756551257</v>
+        <v>-0.09092862395118669</v>
       </c>
       <c r="Z5">
-        <v>0.08612088431444624</v>
+        <v>0.0560356114166012</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08476223205805308</v>
+        <v>0.07244306702476362</v>
       </c>
       <c r="AC5">
-        <v>-0.08476223205805308</v>
+        <v>-0.07244306702476362</v>
       </c>
       <c r="AD5">
-        <v>87.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>87.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG5">
-        <v>86.75999999999999</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.5868983957219251</v>
+        <v>0.7033595425303788</v>
       </c>
       <c r="AI5">
-        <v>0.4167062173706692</v>
+        <v>0.4927391086629945</v>
       </c>
       <c r="AJ5">
-        <v>0.5840064620355411</v>
+        <v>0.6974777664382563</v>
       </c>
       <c r="AK5">
-        <v>0.4138128398359248</v>
+        <v>0.4857345923444004</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Muscat Finance SAOG (MSM:MFCI)</t>
+          <t>National Finance Company SAOG (MSM:NFCI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,10 +1112,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.131</v>
+        <v>0.007650000000000001</v>
       </c>
       <c r="E6">
-        <v>-0.251</v>
+        <v>-0.0267</v>
+      </c>
+      <c r="F6">
+        <v>0.092</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1124,94 +1127,103 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.0004093851468960163</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.0003479773748616138</v>
       </c>
       <c r="K6">
-        <v>2.92</v>
+        <v>29.4</v>
       </c>
       <c r="L6">
-        <v>0.2703703703703704</v>
+        <v>0.4772727272727272</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>11.2</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04527081649151172</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>11.2</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.04527081649151172</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>2.55</v>
+        <v>19.7</v>
       </c>
       <c r="V6">
-        <v>0.04903846153846154</v>
+        <v>0.07962813257881972</v>
       </c>
       <c r="W6">
-        <v>0.02979591836734694</v>
+        <v>0.09842651489789087</v>
       </c>
       <c r="X6">
-        <v>0.08698634875298619</v>
+        <v>0.1177236054335266</v>
       </c>
       <c r="Y6">
-        <v>-0.05719043038563926</v>
+        <v>-0.01929709053563577</v>
       </c>
       <c r="Z6">
-        <v>0.04820998125167397</v>
+        <v>0.06085579993763438</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.117644150740157e-05</v>
       </c>
       <c r="AB6">
-        <v>0.08517062513735672</v>
+        <v>0.07392497637655013</v>
       </c>
       <c r="AC6">
-        <v>-0.08517062513735672</v>
+        <v>-0.07390379993504273</v>
       </c>
       <c r="AD6">
-        <v>92.90000000000001</v>
+        <v>869.9</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.028909374756027</v>
       </c>
       <c r="AF6">
-        <v>92.90000000000001</v>
+        <v>869.928909374756</v>
       </c>
       <c r="AG6">
-        <v>90.35000000000001</v>
+        <v>850.228909374756</v>
       </c>
       <c r="AH6">
-        <v>0.6411318150448585</v>
+        <v>0.7785790755754793</v>
       </c>
       <c r="AI6">
-        <v>0.4801033591731266</v>
+        <v>0.7648877138390842</v>
       </c>
       <c r="AJ6">
-        <v>0.6347031963470319</v>
+        <v>0.7746050619777072</v>
       </c>
       <c r="AK6">
-        <v>0.4731605132233569</v>
+        <v>0.7607434831391453</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>28061.29032258064</v>
+      </c>
+      <c r="AP6">
+        <v>27426.7390120889</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Finance Company SAOG (MSM:NFCI)</t>
+          <t>Taageer Finance Company SAOG (MSM:TFCI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1231,10 +1243,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.15</v>
+        <v>0.073</v>
       </c>
       <c r="E7">
-        <v>0.104</v>
+        <v>0.0344</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1243,34 +1255,34 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.0005488118097140172</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.0004257090991658576</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>25.2</v>
+        <v>9.98</v>
       </c>
       <c r="L7">
-        <v>0.4692737430167597</v>
+        <v>0.3551601423487544</v>
       </c>
       <c r="M7">
-        <v>11.2</v>
+        <v>3.36</v>
       </c>
       <c r="N7">
-        <v>0.06926406926406926</v>
+        <v>0.05161290322580645</v>
       </c>
       <c r="O7">
-        <v>0.4444444444444444</v>
+        <v>0.3366733466933867</v>
       </c>
       <c r="P7">
-        <v>11.2</v>
+        <v>3.36</v>
       </c>
       <c r="Q7">
-        <v>0.06926406926406926</v>
+        <v>0.05161290322580645</v>
       </c>
       <c r="R7">
-        <v>0.4444444444444444</v>
+        <v>0.3366733466933867</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1279,67 +1291,61 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>13</v>
+        <v>40.4</v>
       </c>
       <c r="V7">
-        <v>0.08039579468150897</v>
+        <v>0.620583717357911</v>
       </c>
       <c r="W7">
-        <v>0.08823529411764705</v>
+        <v>0.08429054054054054</v>
       </c>
       <c r="X7">
-        <v>0.1325609006105203</v>
+        <v>0.1656437515998261</v>
       </c>
       <c r="Y7">
-        <v>-0.04432560649287323</v>
+        <v>-0.08135321105928557</v>
       </c>
       <c r="Z7">
-        <v>0.05498935498084655</v>
+        <v>0.06237513873473918</v>
       </c>
       <c r="AA7">
-        <v>2.340946877260775e-05</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09546749606226292</v>
+        <v>0.07561246632783016</v>
       </c>
       <c r="AC7">
-        <v>-0.09544408659349031</v>
+        <v>-0.07561246632783016</v>
       </c>
       <c r="AD7">
-        <v>742</v>
+        <v>414.4</v>
       </c>
       <c r="AE7">
-        <v>0.03264402909178637</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>742.0326440290918</v>
+        <v>414.4</v>
       </c>
       <c r="AG7">
-        <v>729.0326440290918</v>
+        <v>374</v>
       </c>
       <c r="AH7">
-        <v>0.8210754020358318</v>
+        <v>0.8642335766423357</v>
       </c>
       <c r="AI7">
-        <v>0.7129906496988382</v>
+        <v>0.7682610307749351</v>
       </c>
       <c r="AJ7">
-        <v>0.8184640463286773</v>
+        <v>0.8517421999544522</v>
       </c>
       <c r="AK7">
-        <v>0.709360209841165</v>
+        <v>0.749498997995992</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>20611.11111111111</v>
-      </c>
-      <c r="AP7">
-        <v>20250.90677858589</v>
       </c>
     </row>
     <row r="8">
@@ -1350,7 +1356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Taageer Finance Company SAOG (MSM:TFCI)</t>
+          <t>United Finance Company SAOG (MSM:UFCI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1359,10 +1365,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.00216</v>
-      </c>
-      <c r="E8">
-        <v>-0.0771</v>
+        <v>0.184</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1377,28 +1380,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>7.89</v>
+        <v>4.84</v>
       </c>
       <c r="L8">
-        <v>0.3554054054054054</v>
+        <v>0.3432624113475177</v>
       </c>
       <c r="M8">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
       <c r="N8">
-        <v>0.03009118541033435</v>
+        <v>0.04636871508379888</v>
       </c>
       <c r="O8">
-        <v>0.2509505703422053</v>
+        <v>0.5144628099173554</v>
       </c>
       <c r="P8">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
       <c r="Q8">
-        <v>0.03009118541033435</v>
+        <v>0.04636871508379888</v>
       </c>
       <c r="R8">
-        <v>0.2509505703422053</v>
+        <v>0.5144628099173554</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1407,55 +1410,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>24.2</v>
+        <v>3.08</v>
       </c>
       <c r="V8">
-        <v>0.3677811550151976</v>
+        <v>0.05735567970204841</v>
       </c>
       <c r="W8">
-        <v>0.07019572953736654</v>
+        <v>0.03938161106590724</v>
       </c>
       <c r="X8">
-        <v>0.1459929815323023</v>
+        <v>0.09297410271846418</v>
       </c>
       <c r="Y8">
-        <v>-0.07579725199493574</v>
+        <v>-0.05359249165255694</v>
       </c>
       <c r="Z8">
-        <v>0.05521014672966923</v>
+        <v>0.06725174091386053</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.09652063575516864</v>
+        <v>0.07665774572330035</v>
       </c>
       <c r="AC8">
-        <v>-0.09652063575516864</v>
+        <v>-0.07665774572330035</v>
       </c>
       <c r="AD8">
-        <v>356.3</v>
+        <v>109.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>356.3</v>
+        <v>109.8</v>
       </c>
       <c r="AG8">
-        <v>332.1</v>
+        <v>106.72</v>
       </c>
       <c r="AH8">
-        <v>0.8441127694859037</v>
+        <v>0.671559633027523</v>
       </c>
       <c r="AI8">
-        <v>0.7505793132504739</v>
+        <v>0.4662420382165605</v>
       </c>
       <c r="AJ8">
-        <v>0.8346318170394571</v>
+        <v>0.6652537090138386</v>
       </c>
       <c r="AK8">
-        <v>0.7371809100998891</v>
+        <v>0.4591687462352637</v>
       </c>
       <c r="AL8">
         <v>0</v>
